--- a/SS3 models/ETCO/06_Base_Final/bootstrap/01_tables.xlsx
+++ b/SS3 models/ETCO/06_Base_Final/bootstrap/01_tables.xlsx
@@ -6,15 +6,15 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="01_Quants" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="02_RefPoints" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="03_Sensitivies" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="01_Quants" sheetId="7" state="visible" r:id="rId1"/>
+    <sheet name="02_RefPoints" sheetId="8" state="visible" r:id="rId2"/>
+    <sheet name="03_Sensitivies" sheetId="9" state="visible" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="178">
   <si>
     <t xml:space="preserve">YEAR</t>
   </si>
@@ -512,6 +512,42 @@
   </si>
   <si>
     <t xml:space="preserve">0.93 (0.89 - 0.98)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.007 (0.004 - 0.014)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F2025/Fmsy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136 (0.078 - 0.238)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSB2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.46 (7.93 - 26.67)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSB2025/SSBmsst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97 (1.47 - 2.62)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Catch_2023-2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.55 (0.19 - 0.92)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPR_2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.87 (0.79 - 0.94)</t>
   </si>
 </sst>
 </file>
@@ -2209,18 +2245,18 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="B3" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="B4" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5">
@@ -2233,18 +2269,18 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="B6" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="B7" t="s">
-        <v>157</v>
+        <v>173</v>
       </c>
     </row>
     <row r="8">
@@ -2257,10 +2293,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="B9" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
     </row>
     <row r="10">
@@ -2273,10 +2309,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="B11" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>
